--- a/files/九龙-长沙湾-Belgravia Place 第2期.xlsx
+++ b/files/九龙-长沙湾-Belgravia Place 第2期.xlsx
@@ -12015,7 +12015,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
